--- a/通信指令.xlsx
+++ b/通信指令.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="117">
   <si>
     <t>所有数字都默认为16进制表示，省略0x标识，所有数据采用大端模式</t>
   </si>
@@ -335,6 +335,9 @@
     <t>结束反馈</t>
   </si>
   <si>
+    <t>质量测试反馈</t>
+  </si>
+  <si>
     <t>电量反馈</t>
   </si>
   <si>
@@ -371,6 +374,9 @@
 NIRS:08</t>
   </si>
   <si>
+    <t>D2</t>
+  </si>
+  <si>
     <t>n+4</t>
   </si>
   <si>
@@ -380,7 +386,13 @@
     <t>数据帧</t>
   </si>
   <si>
+    <t>D0</t>
+  </si>
+  <si>
     <t>补包帧</t>
+  </si>
+  <si>
+    <t>D1</t>
   </si>
   <si>
     <t>对EEG/sEMG:一个数据包，包含10帧数据，只传输已开启的通道数据，顺序为从小到大排列。</t>
@@ -1733,7 +1745,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1998,9 +2010,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2019,9 +2028,6 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2047,9 +2053,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2498,7 +2501,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X41"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.2583333333333" style="2" customWidth="1"/>
@@ -2653,7 +2656,7 @@
       <c r="B6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="112" t="s">
+      <c r="C6" s="109" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="21" t="s">
@@ -2802,7 +2805,7 @@
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="J9" s="33"/>
-      <c r="M9" s="113" t="s">
+      <c r="M9" s="110" t="s">
         <v>44</v>
       </c>
       <c r="N9" s="43">
@@ -2855,7 +2858,7 @@
       <c r="H10" s="47"/>
       <c r="I10" s="48"/>
       <c r="J10" s="33"/>
-      <c r="M10" s="113" t="s">
+      <c r="M10" s="110" t="s">
         <v>52</v>
       </c>
       <c r="N10" s="43">
@@ -2908,7 +2911,7 @@
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="J11" s="33"/>
-      <c r="M11" s="113" t="s">
+      <c r="M11" s="110" t="s">
         <v>55</v>
       </c>
       <c r="N11" s="43">
@@ -2955,7 +2958,7 @@
         <v>15</v>
       </c>
       <c r="J12" s="33"/>
-      <c r="M12" s="113" t="s">
+      <c r="M12" s="110" t="s">
         <v>61</v>
       </c>
       <c r="N12" s="43">
@@ -3208,7 +3211,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" ht="14.25" spans="1:24">
       <c r="A22" s="28" t="s">
         <v>89</v>
       </c>
@@ -3270,21 +3273,21 @@
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
     </row>
-    <row r="25" spans="1:24">
-      <c r="A25" s="28" t="s">
+    <row r="25" ht="14.25" spans="1:24">
+      <c r="A25" s="44" t="s">
         <v>93</v>
       </c>
       <c r="B25" s="76"/>
       <c r="C25" s="30"/>
       <c r="D25" s="31"/>
       <c r="E25" s="32" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F25" s="32">
         <v>1</v>
       </c>
       <c r="G25" s="32" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
@@ -3294,19 +3297,19 @@
     </row>
     <row r="26" ht="14.25" spans="1:24">
       <c r="A26" s="28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" s="76"/>
       <c r="C26" s="30"/>
       <c r="D26" s="31"/>
       <c r="E26" s="32" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F26" s="32">
         <v>1</v>
       </c>
       <c r="G26" s="32" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
@@ -3314,277 +3317,276 @@
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
     </row>
-    <row r="27" spans="1:24">
-      <c r="A27" s="57" t="s">
+    <row r="27" ht="14.25" spans="1:24">
+      <c r="A27" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="B27" s="77"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="61" t="s">
+      <c r="B27" s="76"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="32">
+        <v>1</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="75"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+    </row>
+    <row r="28" ht="14.25" spans="1:24">
+      <c r="A28" s="57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="77"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="F27" s="61">
+      <c r="F28" s="61">
         <v>1</v>
       </c>
-      <c r="G27" s="61" t="s">
+      <c r="G28" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="78"/>
-      <c r="R27" s="79"/>
-      <c r="S27" s="79"/>
-    </row>
-    <row r="28" ht="15"/>
-    <row r="29" s="1" customFormat="1" ht="15" spans="1:24">
-      <c r="A29" s="80" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="81"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="81"/>
-      <c r="K29" s="82"/>
-      <c r="M29" s="83"/>
-    </row>
-    <row r="30" ht="15" spans="1:24">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11" t="s">
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="78"/>
+      <c r="R28" s="79"/>
+      <c r="S28" s="79"/>
+    </row>
+    <row r="29" ht="15"/>
+    <row r="30" s="1" customFormat="1" ht="15" spans="1:24">
+      <c r="A30" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="81"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="82"/>
+      <c r="M30" s="83"/>
+    </row>
+    <row r="31" ht="15" spans="1:24">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C31" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="11" t="s">
+      <c r="D31" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F31" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G31" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K30" s="85" t="s">
+      <c r="H31" s="11"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="K31" s="85" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" ht="15" spans="1:24">
-      <c r="A31" s="68"/>
-      <c r="B31" s="69" t="s">
+    <row r="32" ht="15" spans="1:24">
+      <c r="A32" s="68"/>
+      <c r="B32" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="69" t="s">
+      <c r="C32" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="69" t="s">
+      <c r="D32" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="69" t="s">
+      <c r="E32" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="69" t="s">
+      <c r="F32" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="G31" s="69" t="s">
+      <c r="G32" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="H32" s="69"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="K32" s="87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" ht="15" spans="1:18">
+      <c r="A33" s="70" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="90" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33" s="92" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="H31" s="69"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="69" t="s">
-        <v>101</v>
-      </c>
-      <c r="K31" s="87" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="1:24">
-      <c r="A32" s="88" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" s="89" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" s="90" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="91" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G32" s="93" t="s">
-        <v>105</v>
-      </c>
-      <c r="H32" s="93"/>
-      <c r="I32" s="93"/>
-      <c r="J32" s="94" t="s">
-        <v>99</v>
-      </c>
-      <c r="K32" s="95" t="s">
+      <c r="K33" s="75" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" spans="1:18">
-      <c r="A33" s="70" t="s">
-        <v>106</v>
-      </c>
-      <c r="B33" s="89"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="93"/>
-      <c r="H33" s="93"/>
-      <c r="I33" s="93"/>
-      <c r="J33" s="97"/>
-      <c r="K33" s="95"/>
-    </row>
     <row r="34" ht="30" customHeight="1" spans="1:18">
-      <c r="A34" s="57" t="s">
-        <v>107</v>
-      </c>
-      <c r="B34" s="98"/>
-      <c r="C34" s="99"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="101" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" s="102"/>
-      <c r="G34" s="103"/>
-      <c r="H34" s="103"/>
-      <c r="I34" s="103"/>
-      <c r="J34" s="104"/>
-      <c r="K34" s="105"/>
-    </row>
-    <row r="35" ht="14.25"/>
-    <row r="36" spans="1:18">
-      <c r="A36" s="106" t="s">
+      <c r="A34" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="106"/>
-      <c r="C36" s="106"/>
-      <c r="D36" s="106"/>
-      <c r="E36" s="106"/>
-      <c r="F36" s="106"/>
-      <c r="G36" s="106"/>
-      <c r="H36" s="106"/>
-      <c r="I36" s="106"/>
-      <c r="J36" s="106"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="107"/>
-      <c r="M36" s="107"/>
-      <c r="N36" s="107"/>
-      <c r="O36" s="107"/>
-      <c r="P36" s="107"/>
-      <c r="Q36" s="107"/>
-    </row>
+      <c r="B34" s="88"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G34" s="92"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="75"/>
+    </row>
+    <row r="35" ht="30" customHeight="1" spans="1:18">
+      <c r="A35" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="96"/>
+      <c r="C35" s="97"/>
+      <c r="D35" s="98"/>
+      <c r="E35" s="99" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="100"/>
+      <c r="G35" s="101"/>
+      <c r="H35" s="101"/>
+      <c r="I35" s="101"/>
+      <c r="J35" s="102"/>
+      <c r="K35" s="78"/>
+    </row>
+    <row r="36" ht="14.25"/>
     <row r="37" spans="1:18">
-      <c r="A37" s="106" t="s">
-        <v>109</v>
-      </c>
-      <c r="B37" s="106"/>
-      <c r="C37" s="106"/>
-      <c r="D37" s="106"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="106"/>
-      <c r="G37" s="106"/>
-      <c r="H37" s="106"/>
-      <c r="I37" s="106"/>
-      <c r="J37" s="106"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="107"/>
-      <c r="M37" s="107"/>
-      <c r="N37" s="107"/>
-      <c r="O37" s="107"/>
-      <c r="P37" s="107"/>
-      <c r="Q37" s="107"/>
+      <c r="A37" s="103" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="103"/>
+      <c r="C37" s="103"/>
+      <c r="D37" s="103"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="103"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="103"/>
+      <c r="J37" s="103"/>
+      <c r="K37" s="103"/>
+      <c r="L37" s="104"/>
+      <c r="M37" s="104"/>
+      <c r="N37" s="104"/>
+      <c r="O37" s="104"/>
+      <c r="P37" s="104"/>
+      <c r="Q37" s="104"/>
     </row>
     <row r="38" spans="1:18">
-      <c r="A38" s="108"/>
-      <c r="B38" s="108"/>
-      <c r="C38" s="108"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108"/>
-      <c r="F38" s="108"/>
-      <c r="G38" s="108"/>
-      <c r="H38" s="108"/>
-      <c r="I38" s="108"/>
-      <c r="J38" s="108"/>
-      <c r="K38" s="108"/>
-      <c r="L38" s="108"/>
-      <c r="M38" s="108"/>
-      <c r="N38" s="108"/>
-      <c r="O38" s="108"/>
-      <c r="P38" s="108"/>
-      <c r="Q38" s="108"/>
+      <c r="A38" s="103" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="103"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="103"/>
+      <c r="H38" s="103"/>
+      <c r="I38" s="103"/>
+      <c r="J38" s="103"/>
+      <c r="K38" s="103"/>
+      <c r="L38" s="104"/>
+      <c r="M38" s="104"/>
+      <c r="N38" s="104"/>
+      <c r="O38" s="104"/>
+      <c r="P38" s="104"/>
+      <c r="Q38" s="104"/>
     </row>
     <row r="39" spans="1:18">
-      <c r="A39" s="109" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" s="110"/>
-      <c r="C39" s="110"/>
-      <c r="D39" s="110"/>
-      <c r="E39" s="110"/>
-      <c r="F39" s="110"/>
-      <c r="G39" s="110"/>
-      <c r="H39" s="110"/>
-      <c r="I39" s="110"/>
-      <c r="J39" s="110"/>
-      <c r="K39" s="110"/>
-      <c r="L39" s="110"/>
-      <c r="M39" s="110"/>
-      <c r="N39" s="110"/>
-      <c r="O39" s="110"/>
-      <c r="P39" s="110"/>
-      <c r="Q39" s="110"/>
-      <c r="R39" s="111"/>
+      <c r="A39" s="105"/>
+      <c r="B39" s="105"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="105"/>
+      <c r="E39" s="105"/>
+      <c r="F39" s="105"/>
+      <c r="G39" s="105"/>
+      <c r="H39" s="105"/>
+      <c r="I39" s="105"/>
+      <c r="J39" s="105"/>
+      <c r="K39" s="105"/>
+      <c r="L39" s="105"/>
+      <c r="M39" s="105"/>
+      <c r="N39" s="105"/>
+      <c r="O39" s="105"/>
+      <c r="P39" s="105"/>
+      <c r="Q39" s="105"/>
     </row>
     <row r="40" spans="1:18">
-      <c r="A40" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="66"/>
-      <c r="M40" s="66"/>
-      <c r="N40" s="66"/>
-      <c r="O40" s="66"/>
-      <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
-      <c r="R40" s="66"/>
+      <c r="A40" s="106" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" s="107"/>
+      <c r="C40" s="107"/>
+      <c r="D40" s="107"/>
+      <c r="E40" s="107"/>
+      <c r="F40" s="107"/>
+      <c r="G40" s="107"/>
+      <c r="H40" s="107"/>
+      <c r="I40" s="107"/>
+      <c r="J40" s="107"/>
+      <c r="K40" s="107"/>
+      <c r="L40" s="107"/>
+      <c r="M40" s="107"/>
+      <c r="N40" s="107"/>
+      <c r="O40" s="107"/>
+      <c r="P40" s="107"/>
+      <c r="Q40" s="107"/>
+      <c r="R40" s="108"/>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="66" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B41" s="66"/>
       <c r="C41" s="66"/>
@@ -3604,8 +3606,30 @@
       <c r="Q41" s="66"/>
       <c r="R41" s="66"/>
     </row>
+    <row r="42" spans="1:18">
+      <c r="A42" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66"/>
+      <c r="J42" s="66"/>
+      <c r="K42" s="66"/>
+      <c r="L42" s="66"/>
+      <c r="M42" s="66"/>
+      <c r="N42" s="66"/>
+      <c r="O42" s="66"/>
+      <c r="P42" s="66"/>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="66"/>
+    </row>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="74">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
@@ -3655,30 +3679,31 @@
     <mergeCell ref="G25:I25"/>
     <mergeCell ref="G26:I26"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="A30:K30"/>
     <mergeCell ref="G31:I31"/>
-    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="G32:I32"/>
     <mergeCell ref="A37:K37"/>
-    <mergeCell ref="A38:Q38"/>
-    <mergeCell ref="A39:R39"/>
-    <mergeCell ref="A40:Q40"/>
-    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A39:Q39"/>
+    <mergeCell ref="A40:R40"/>
+    <mergeCell ref="A41:Q41"/>
+    <mergeCell ref="A42:R42"/>
     <mergeCell ref="B6:B14"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="B21:B28"/>
+    <mergeCell ref="B33:B35"/>
     <mergeCell ref="C7:C14"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C21:C28"/>
+    <mergeCell ref="C33:C35"/>
     <mergeCell ref="D6:D14"/>
-    <mergeCell ref="D21:D27"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="D21:D28"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="F33:F35"/>
     <mergeCell ref="J6:J14"/>
-    <mergeCell ref="J21:J27"/>
-    <mergeCell ref="J32:J34"/>
-    <mergeCell ref="K32:K34"/>
-    <mergeCell ref="G32:I34"/>
+    <mergeCell ref="J21:J28"/>
+    <mergeCell ref="J33:J35"/>
+    <mergeCell ref="K33:K35"/>
+    <mergeCell ref="G33:I35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
